--- a/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_02-09-2026.xlsx
+++ b/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_02-09-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Ecotherm_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70D8ECE0-FE45-4024-9770-6F96E45615D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{907DEBFB-D72B-45D8-BA17-D77176D95B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32220" yWindow="2535" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="35310" yWindow="1680" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
